--- a/themes/payment.xlsx
+++ b/themes/payment.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,27 +450,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Платеж по кредиту списывается в дату платежа. Обычно это происходит в ночь при закрытии банковского дня</t>
+          <t xml:space="preserve">            1. В вверху главной страницы приложения выберите «Оплата по QR».</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Платеж по кредиту списывается в дату платежа. Обычно это происходит в ночь при закрытии банковского дня.</t>
+          <t xml:space="preserve">            1. Вверху главной страницы приложения выберите «Оплата по QR».</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>убрано лишнее «В» перед «вверху» (дублирование предлога)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -484,45 +484,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>убрано лишнее «В» перед «вверху» (дублирование предлога)</t>
+          <t>убрано лишнее «В» перед «вверху» (дублирование предлога) — для единообразия с аналогичным пунктом выше (стр. 106)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            1. В вверху главной страницы приложения выберите «Оплата по QR».</t>
+          <t xml:space="preserve">    Authorized: Для решения проблем при оплате по QR коду перевожу вас на оператора. Пожалуйста, ожидайте.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">            1. Вверху главной страницы приложения выберите «Оплата по QR».</t>
+          <t xml:space="preserve">    Authorized: Для решения проблем при оплате по QR-коду перевожу вас на оператора. Пожалуйста, ожидайте.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>убрано лишнее «В» перед «вверху» (дублирование предлога) — для единообразия с аналогичным пунктом выше (стр. 106)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>119</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Authorized: Для решения проблем при оплате по QR коду перевожу вас на оператора. Пожалуйста, ожидайте.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Authorized: Для решения проблем при оплате по QR-коду перевожу вас на оператора. Пожалуйста, ожидайте.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
         <is>
           <t>добавлен дефис «QR-коду» — для единообразия с остальными случаями в файле</t>
         </is>
